--- a/Selenium_Test_Report_300.xlsx
+++ b/Selenium_Test_Report_300.xlsx
@@ -573,7 +573,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Execution Date: 2026-08-27 10:47:01</t>
+          <t>Execution Date: 2026-08-27 11:54:35</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>~11.65 seconds</t>
+          <t>~11.86 seconds</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="K2" s="7" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="K3" s="10" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="K4" s="7" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="K5" s="10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="K6" s="7" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="K7" s="10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="K8" s="7" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="K9" s="10" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L9" s="10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="K10" s="7" t="n">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         </is>
       </c>
       <c r="K11" s="10" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="K12" s="7" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="K13" s="10" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="K14" s="7" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="K15" s="10" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="K16" s="7" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="K17" s="10" t="n">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="K18" s="7" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="K19" s="10" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="K20" s="7" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="K21" s="10" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="K22" s="7" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="K23" s="10" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="K24" s="7" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="K25" s="10" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="K26" s="7" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="K27" s="10" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="K28" s="7" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="K29" s="10" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="K30" s="7" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="K31" s="10" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="K32" s="7" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="K33" s="10" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="L33" s="10" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="K34" s="7" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="K35" s="10" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="L35" s="10" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="K36" s="7" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="K37" s="10" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="L37" s="10" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="K38" s="7" t="n">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="K39" s="10" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="L39" s="10" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="K40" s="7" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="K41" s="10" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L41" s="10" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="K42" s="7" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="K43" s="10" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L43" s="10" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="K44" s="7" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="K45" s="10" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="L45" s="10" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="K46" s="7" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="K47" s="10" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="L47" s="10" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="K48" s="7" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="K49" s="10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="L49" s="10" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="K50" s="7" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="K51" s="10" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="L51" s="10" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="K52" s="7" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="K53" s="10" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="L53" s="10" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="K54" s="7" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="K55" s="10" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="L55" s="10" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="K56" s="7" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="K57" s="10" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="L57" s="10" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="K58" s="7" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="K59" s="10" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="L59" s="10" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="K60" s="7" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         </is>
       </c>
       <c r="K61" s="10" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L61" s="10" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="K62" s="7" t="n">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="K63" s="10" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L63" s="10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="K64" s="7" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="K65" s="10" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="L65" s="10" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         </is>
       </c>
       <c r="K66" s="7" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="K67" s="10" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="L67" s="10" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         </is>
       </c>
       <c r="K69" s="10" t="n">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="L69" s="10" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="K70" s="7" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="K71" s="10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L71" s="10" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="K72" s="7" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="K73" s="10" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="L73" s="10" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="K74" s="7" t="n">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="K75" s="10" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L75" s="10" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         </is>
       </c>
       <c r="K76" s="7" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="K77" s="10" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="L77" s="10" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         </is>
       </c>
       <c r="K78" s="7" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="K79" s="10" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="L79" s="10" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="K80" s="7" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="K81" s="10" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="L81" s="10" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         </is>
       </c>
       <c r="K82" s="7" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="K83" s="10" t="n">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         </is>
       </c>
       <c r="K84" s="7" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="K85" s="10" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L85" s="10" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         </is>
       </c>
       <c r="K86" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         </is>
       </c>
       <c r="K87" s="10" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L87" s="10" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="K88" s="7" t="n">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         </is>
       </c>
       <c r="K89" s="10" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="L89" s="10" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         </is>
       </c>
       <c r="K90" s="7" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="K91" s="10" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L91" s="10" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="K92" s="7" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="K93" s="10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L93" s="10" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         </is>
       </c>
       <c r="K94" s="7" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         </is>
       </c>
       <c r="K95" s="10" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="L95" s="10" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         </is>
       </c>
       <c r="K96" s="7" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="K97" s="10" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="L97" s="10" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="K98" s="7" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="K99" s="10" t="n">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="L99" s="10" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="K100" s="7" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         </is>
       </c>
       <c r="K101" s="10" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="L101" s="10" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="K102" s="7" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="K103" s="10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L103" s="10" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="K104" s="7" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         </is>
       </c>
       <c r="K105" s="10" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L105" s="10" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="K106" s="7" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="K107" s="10" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="L107" s="10" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="K108" s="7" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="K109" s="10" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="L109" s="10" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         </is>
       </c>
       <c r="K110" s="7" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="K111" s="10" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="L111" s="10" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         </is>
       </c>
       <c r="K112" s="7" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="K113" s="10" t="n">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="L113" s="10" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="K114" s="7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="K115" s="10" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="L115" s="10" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         </is>
       </c>
       <c r="K116" s="7" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="K117" s="10" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="L117" s="10" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         </is>
       </c>
       <c r="K118" s="7" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="K119" s="10" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="L119" s="10" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="K120" s="7" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         </is>
       </c>
       <c r="K121" s="10" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="L121" s="10" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         </is>
       </c>
       <c r="K122" s="7" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="K123" s="10" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L123" s="10" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="K124" s="7" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         </is>
       </c>
       <c r="K125" s="10" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="L125" s="10" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         </is>
       </c>
       <c r="K126" s="7" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="K127" s="10" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="L127" s="10" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         </is>
       </c>
       <c r="K128" s="7" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="K129" s="10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L129" s="10" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         </is>
       </c>
       <c r="K130" s="7" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="K131" s="10" t="n">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="L131" s="10" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         </is>
       </c>
       <c r="K132" s="7" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
         </is>
       </c>
       <c r="K133" s="10" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="L133" s="10" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         </is>
       </c>
       <c r="K134" s="7" t="n">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="K135" s="10" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="L135" s="10" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         </is>
       </c>
       <c r="K136" s="7" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="K137" s="10" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="L137" s="10" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="K138" s="7" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         </is>
       </c>
       <c r="K139" s="10" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="L139" s="10" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         </is>
       </c>
       <c r="K140" s="7" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         </is>
       </c>
       <c r="K141" s="10" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="L141" s="10" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         </is>
       </c>
       <c r="K142" s="7" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         </is>
       </c>
       <c r="K143" s="10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L143" s="10" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         </is>
       </c>
       <c r="K144" s="7" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         </is>
       </c>
       <c r="K145" s="10" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="L145" s="10" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         </is>
       </c>
       <c r="K146" s="7" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         </is>
       </c>
       <c r="K147" s="10" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="L147" s="10" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="K148" s="7" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="K149" s="10" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="L149" s="10" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         </is>
       </c>
       <c r="K150" s="7" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         </is>
       </c>
       <c r="K151" s="10" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="L151" s="10" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         </is>
       </c>
       <c r="K152" s="7" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         </is>
       </c>
       <c r="K153" s="10" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="L153" s="10" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="K154" s="7" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="L154" s="7" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         </is>
       </c>
       <c r="K155" s="10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="L155" s="10" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         </is>
       </c>
       <c r="K156" s="7" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         </is>
       </c>
       <c r="K157" s="10" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="L157" s="10" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         </is>
       </c>
       <c r="K158" s="7" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="L158" s="7" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         </is>
       </c>
       <c r="K160" s="7" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="L160" s="7" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="K161" s="10" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="L161" s="10" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="K162" s="7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L162" s="7" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         </is>
       </c>
       <c r="K163" s="10" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="L163" s="10" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         </is>
       </c>
       <c r="K164" s="7" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         </is>
       </c>
       <c r="K165" s="10" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L165" s="10" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         </is>
       </c>
       <c r="K166" s="7" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         </is>
       </c>
       <c r="K167" s="10" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L167" s="10" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="K168" s="7" t="n">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="L168" s="7" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         </is>
       </c>
       <c r="K169" s="10" t="n">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="L169" s="10" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         </is>
       </c>
       <c r="K170" s="7" t="n">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="L170" s="7" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         </is>
       </c>
       <c r="K171" s="10" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="L171" s="10" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="K172" s="7" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="L172" s="7" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         </is>
       </c>
       <c r="K173" s="10" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="L173" s="10" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         </is>
       </c>
       <c r="K174" s="7" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="L174" s="7" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         </is>
       </c>
       <c r="K175" s="10" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="L175" s="10" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         </is>
       </c>
       <c r="K176" s="7" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="L176" s="7" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         </is>
       </c>
       <c r="K177" s="10" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="L177" s="10" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         </is>
       </c>
       <c r="K178" s="7" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L178" s="7" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="K179" s="10" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="L179" s="10" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         </is>
       </c>
       <c r="K180" s="7" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L180" s="7" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         </is>
       </c>
       <c r="K181" s="10" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="L181" s="10" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         </is>
       </c>
       <c r="K182" s="7" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="L182" s="7" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         </is>
       </c>
       <c r="K183" s="10" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="L183" s="10" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         </is>
       </c>
       <c r="K184" s="7" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="L184" s="7" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
         </is>
       </c>
       <c r="K185" s="10" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="L185" s="10" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         </is>
       </c>
       <c r="K186" s="7" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L186" s="7" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         </is>
       </c>
       <c r="K187" s="10" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="L187" s="10" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         </is>
       </c>
       <c r="K188" s="7" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="L188" s="7" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         </is>
       </c>
       <c r="K189" s="10" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="L189" s="10" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         </is>
       </c>
       <c r="K190" s="7" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="L190" s="7" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         </is>
       </c>
       <c r="K191" s="10" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L191" s="10" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         </is>
       </c>
       <c r="K192" s="7" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="L192" s="7" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         </is>
       </c>
       <c r="K193" s="10" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="L193" s="10" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         </is>
       </c>
       <c r="K194" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L194" s="7" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         </is>
       </c>
       <c r="K195" s="10" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="L195" s="10" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="K196" s="7" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="L196" s="7" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         </is>
       </c>
       <c r="K198" s="7" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="L198" s="7" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="K199" s="10" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="L199" s="10" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         </is>
       </c>
       <c r="K201" s="10" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="L201" s="10" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         </is>
       </c>
       <c r="K202" s="7" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="L202" s="7" t="inlineStr">
         <is>
@@ -13815,7 +13815,7 @@
         </is>
       </c>
       <c r="K203" s="10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L203" s="10" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         </is>
       </c>
       <c r="K204" s="7" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="L204" s="7" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         </is>
       </c>
       <c r="K205" s="10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L205" s="10" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         </is>
       </c>
       <c r="K206" s="7" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L206" s="7" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         </is>
       </c>
       <c r="K207" s="10" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="L207" s="10" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         </is>
       </c>
       <c r="K208" s="7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L208" s="7" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         </is>
       </c>
       <c r="K209" s="10" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L209" s="10" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         </is>
       </c>
       <c r="K210" s="7" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="L210" s="7" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="K211" s="10" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="L211" s="10" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         </is>
       </c>
       <c r="K212" s="7" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="L212" s="7" t="inlineStr">
         <is>
@@ -14445,7 +14445,7 @@
         </is>
       </c>
       <c r="K213" s="10" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="L213" s="10" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         </is>
       </c>
       <c r="K214" s="7" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L214" s="7" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         </is>
       </c>
       <c r="K215" s="10" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="L215" s="10" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         </is>
       </c>
       <c r="K216" s="7" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="L216" s="7" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         </is>
       </c>
       <c r="K217" s="10" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="L217" s="10" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         </is>
       </c>
       <c r="K218" s="7" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="L218" s="7" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         </is>
       </c>
       <c r="K219" s="10" t="n">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="L219" s="10" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         </is>
       </c>
       <c r="K220" s="7" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="L220" s="7" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         </is>
       </c>
       <c r="K221" s="10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L221" s="10" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         </is>
       </c>
       <c r="K222" s="7" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="L222" s="7" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         </is>
       </c>
       <c r="K223" s="10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L223" s="10" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         </is>
       </c>
       <c r="K224" s="7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="L224" s="7" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         </is>
       </c>
       <c r="K225" s="10" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="L225" s="10" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         </is>
       </c>
       <c r="K226" s="7" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="L226" s="7" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         </is>
       </c>
       <c r="K227" s="10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="L227" s="10" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         </is>
       </c>
       <c r="K228" s="7" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="L228" s="7" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="K229" s="10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L229" s="10" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         </is>
       </c>
       <c r="K230" s="7" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="L230" s="7" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         </is>
       </c>
       <c r="K231" s="10" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="L231" s="10" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         </is>
       </c>
       <c r="K232" s="7" t="n">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="L232" s="7" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         </is>
       </c>
       <c r="K233" s="10" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="L233" s="10" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         </is>
       </c>
       <c r="K234" s="7" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="L234" s="7" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         </is>
       </c>
       <c r="K235" s="10" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="L235" s="10" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         </is>
       </c>
       <c r="K236" s="7" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="L236" s="7" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="K237" s="10" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="L237" s="10" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         </is>
       </c>
       <c r="K238" s="7" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="L238" s="7" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         </is>
       </c>
       <c r="K239" s="10" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="L239" s="10" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         </is>
       </c>
       <c r="K240" s="7" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="L240" s="7" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         </is>
       </c>
       <c r="K241" s="10" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="L241" s="10" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         </is>
       </c>
       <c r="K242" s="7" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="L242" s="7" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         </is>
       </c>
       <c r="K243" s="10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L243" s="10" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         </is>
       </c>
       <c r="K244" s="7" t="n">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="L244" s="7" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         </is>
       </c>
       <c r="K245" s="10" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="L245" s="10" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         </is>
       </c>
       <c r="K246" s="7" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="L246" s="7" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         </is>
       </c>
       <c r="K247" s="10" t="n">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="L247" s="10" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         </is>
       </c>
       <c r="K248" s="7" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="L248" s="7" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="K249" s="10" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="L249" s="10" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         </is>
       </c>
       <c r="K250" s="7" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L250" s="7" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         </is>
       </c>
       <c r="K251" s="10" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="L251" s="10" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         </is>
       </c>
       <c r="K252" s="7" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="L252" s="7" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         </is>
       </c>
       <c r="K253" s="10" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L253" s="10" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="K254" s="7" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="L254" s="7" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         </is>
       </c>
       <c r="K255" s="10" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="L255" s="10" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         </is>
       </c>
       <c r="K256" s="7" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="L256" s="7" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         </is>
       </c>
       <c r="K257" s="10" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="L257" s="10" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         </is>
       </c>
       <c r="K258" s="7" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="L258" s="7" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         </is>
       </c>
       <c r="K259" s="10" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="L259" s="10" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         </is>
       </c>
       <c r="K260" s="7" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L260" s="7" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         </is>
       </c>
       <c r="K261" s="10" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="L261" s="10" t="inlineStr">
         <is>
@@ -17532,7 +17532,7 @@
         </is>
       </c>
       <c r="K262" s="7" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="L262" s="7" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         </is>
       </c>
       <c r="K263" s="10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L263" s="10" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         </is>
       </c>
       <c r="K264" s="7" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="L264" s="7" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         </is>
       </c>
       <c r="K265" s="10" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="L265" s="10" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         </is>
       </c>
       <c r="K266" s="7" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="L266" s="7" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         </is>
       </c>
       <c r="K267" s="10" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="L267" s="10" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         </is>
       </c>
       <c r="K268" s="7" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L268" s="7" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         </is>
       </c>
       <c r="K269" s="10" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="L269" s="10" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         </is>
       </c>
       <c r="K270" s="7" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="L270" s="7" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         </is>
       </c>
       <c r="K271" s="10" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="L271" s="10" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         </is>
       </c>
       <c r="K272" s="7" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L272" s="7" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         </is>
       </c>
       <c r="K273" s="10" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="L273" s="10" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         </is>
       </c>
       <c r="K274" s="7" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L274" s="7" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         </is>
       </c>
       <c r="K275" s="10" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="L275" s="10" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         </is>
       </c>
       <c r="K276" s="7" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L276" s="7" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         </is>
       </c>
       <c r="K277" s="10" t="n">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="L277" s="10" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         </is>
       </c>
       <c r="K278" s="7" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="L278" s="7" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="K279" s="10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L279" s="10" t="inlineStr">
         <is>
@@ -18666,7 +18666,7 @@
         </is>
       </c>
       <c r="K280" s="7" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="L280" s="7" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         </is>
       </c>
       <c r="K281" s="10" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="L281" s="10" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         </is>
       </c>
       <c r="K282" s="7" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="L282" s="7" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         </is>
       </c>
       <c r="K283" s="10" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L283" s="10" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         </is>
       </c>
       <c r="K284" s="7" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L284" s="7" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         </is>
       </c>
       <c r="K285" s="10" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="L285" s="10" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         </is>
       </c>
       <c r="K286" s="7" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="L286" s="7" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         </is>
       </c>
       <c r="K287" s="10" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="L287" s="10" t="inlineStr">
         <is>
@@ -19170,7 +19170,7 @@
         </is>
       </c>
       <c r="K288" s="7" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="L288" s="7" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         </is>
       </c>
       <c r="K289" s="10" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="L289" s="10" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="K290" s="7" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="L290" s="7" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         </is>
       </c>
       <c r="K291" s="10" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="L291" s="10" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="K292" s="7" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="L292" s="7" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         </is>
       </c>
       <c r="K293" s="10" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="L293" s="10" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         </is>
       </c>
       <c r="K294" s="7" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="L294" s="7" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         </is>
       </c>
       <c r="K295" s="10" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L295" s="10" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         </is>
       </c>
       <c r="K296" s="7" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L296" s="7" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         </is>
       </c>
       <c r="K297" s="10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L297" s="10" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         </is>
       </c>
       <c r="K299" s="10" t="n">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="L299" s="10" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         </is>
       </c>
       <c r="K300" s="7" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L300" s="7" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         </is>
       </c>
       <c r="K301" s="10" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L301" s="10" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         </is>
       </c>
       <c r="K302" s="7" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="L302" s="7" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         </is>
       </c>
       <c r="K303" s="10" t="n">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="L303" s="10" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         </is>
       </c>
       <c r="K304" s="7" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="L304" s="7" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
         </is>
       </c>
       <c r="K305" s="10" t="n">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="L305" s="10" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         </is>
       </c>
       <c r="K306" s="7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L306" s="7" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         </is>
       </c>
       <c r="K307" s="10" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L307" s="10" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         </is>
       </c>
       <c r="K308" s="7" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L308" s="7" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         </is>
       </c>
       <c r="K309" s="10" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="L309" s="10" t="inlineStr">
         <is>
